--- a/scripts/visitados/salida.xlsx
+++ b/scripts/visitados/salida.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/62582315a8a39068/Trabajo IM/APP/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/62582315a8a39068/Trabajo IM/APP/scripts/visitados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_95DEF3875F2A8FE430B40D2F5EF00BE94DD9B403" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE9303CF-B762-42C9-8417-8312AA58EFFB}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_95DEF3875F2A8FE430B40D2F5EF00BE94DD9B403" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{617D4379-FBAE-4396-B425-8AB846F09435}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DB" sheetId="1" r:id="rId1"/>
@@ -1670,7 +1670,7 @@
   <dimension ref="A1:I2073"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" customWidth="1"/>
     <col min="3" max="3" width="9.7109375" customWidth="1"/>
     <col min="4" max="4" width="12.7109375" customWidth="1"/>
